--- a/data/trans_orig/P1804_2016_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1804_2016_2023-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20565</t>
+          <t>20721</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43694</t>
+          <t>42180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59110</t>
+          <t>58921</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57907</t>
+          <t>60387</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91757</t>
+          <t>93616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>631106</t>
+          <t>632620</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>654235</t>
+          <t>654079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>613729</t>
+          <t>613918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>641173</t>
+          <t>638838</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1255882</t>
+          <t>1254023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1289732</t>
+          <t>1287252</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44882</t>
+          <t>44375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73811</t>
+          <t>74180</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73680</t>
+          <t>72302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>111231</t>
+          <t>110627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124959</t>
+          <t>127004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>171575</t>
+          <t>175755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>948620</t>
+          <t>948251</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>977549</t>
+          <t>978056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>931682</t>
+          <t>932286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>969233</t>
+          <t>970611</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1893769</t>
+          <t>1889589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1940385</t>
+          <t>1938340</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27835</t>
+          <t>29051</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53598</t>
+          <t>54843</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73777</t>
+          <t>73917</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110663</t>
+          <t>109463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111868</t>
+          <t>109639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157239</t>
+          <t>156762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>705954</t>
+          <t>704709</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>731717</t>
+          <t>730501</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>674348</t>
+          <t>675548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>711234</t>
+          <t>711094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1387324</t>
+          <t>1387801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1432695</t>
+          <t>1434924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67634</t>
+          <t>69128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102606</t>
+          <t>103242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105484</t>
+          <t>104283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151849</t>
+          <t>148721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>185006</t>
+          <t>183607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242425</t>
+          <t>244296</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>834961</t>
+          <t>834325</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869933</t>
+          <t>868439</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>891930</t>
+          <t>895058</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>938295</t>
+          <t>939496</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1738921</t>
+          <t>1737050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1796340</t>
+          <t>1797739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>186939</t>
+          <t>184751</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>246481</t>
+          <t>243225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>322187</t>
+          <t>312856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>391829</t>
+          <t>388852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>520169</t>
+          <t>515476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>614524</t>
+          <t>615517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3147869</t>
+          <t>3151125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3207411</t>
+          <t>3209599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3152713</t>
+          <t>3155690</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3222355</t>
+          <t>3231686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6324368</t>
+          <t>6323375</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6418723</t>
+          <t>6423416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -2673,32 +2673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22268</t>
+          <t>24653</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37586</t>
+          <t>42011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2708,32 +2708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42480</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32276</t>
+          <t>34402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56676</t>
+          <t>62245</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2743,32 +2743,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>64748</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49138</t>
+          <t>55791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82345</t>
+          <t>93159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>613173</t>
+          <t>666057</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>597855</t>
+          <t>648699</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>621886</t>
+          <t>675624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2821,32 +2821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>632770</t>
+          <t>684941</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>618574</t>
+          <t>670329</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>642974</t>
+          <t>698172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2856,32 +2856,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1245943</t>
+          <t>1350999</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1228346</t>
+          <t>1330125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1261553</t>
+          <t>1367493</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -2899,17 +2899,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675250</t>
+          <t>732574</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675250</t>
+          <t>732574</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675250</t>
+          <t>732574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310691</t>
+          <t>1423284</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310691</t>
+          <t>1423284</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310691</t>
+          <t>1423284</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71399</t>
+          <t>88990</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>68423</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99349</t>
+          <t>114240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83205</t>
+          <t>95341</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67816</t>
+          <t>79030</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99760</t>
+          <t>115643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>154604</t>
+          <t>184330</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101121</t>
+          <t>159033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>186853</t>
+          <t>213031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3129,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1121465</t>
+          <t>959927</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1093515</t>
+          <t>934677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1157449</t>
+          <t>980494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>874901</t>
+          <t>975497</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>858346</t>
+          <t>955195</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>890290</t>
+          <t>991808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1996367</t>
+          <t>1935425</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1964118</t>
+          <t>1906724</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2049850</t>
+          <t>1960722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3359,32 +3359,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19887</t>
+          <t>24395</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>16725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>36046</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38588</t>
+          <t>49532</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>39054</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55249</t>
+          <t>66019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3429,32 +3429,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>58475</t>
+          <t>73927</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38033</t>
+          <t>59696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75768</t>
+          <t>91801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -3472,32 +3472,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>684793</t>
+          <t>778678</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>675341</t>
+          <t>767027</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>691796</t>
+          <t>786348</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3507,32 +3507,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>891660</t>
+          <t>756588</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>874999</t>
+          <t>740101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>909889</t>
+          <t>767066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1576453</t>
+          <t>1535266</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1559160</t>
+          <t>1517392</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1596895</t>
+          <t>1549497</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>930248</t>
+          <t>806120</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>930248</t>
+          <t>806120</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>930248</t>
+          <t>806120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634928</t>
+          <t>1609193</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634928</t>
+          <t>1609193</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634928</t>
+          <t>1609193</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3702,32 +3702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77281</t>
+          <t>80530</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62135</t>
+          <t>66020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95555</t>
+          <t>100495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>112455</t>
+          <t>125327</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88595</t>
+          <t>109417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132906</t>
+          <t>146867</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3772,32 +3772,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>189736</t>
+          <t>205856</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164731</t>
+          <t>182058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>215654</t>
+          <t>230446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -3815,32 +3815,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>849550</t>
+          <t>909532</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831276</t>
+          <t>889567</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>864696</t>
+          <t>924042</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>981799</t>
+          <t>993030</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>961348</t>
+          <t>971490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1005659</t>
+          <t>1008940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3885,32 +3885,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1831349</t>
+          <t>1902563</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1805431</t>
+          <t>1877973</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1856354</t>
+          <t>1926361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -3928,17 +3928,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094254</t>
+          <t>1118357</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3998,17 +3998,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021085</t>
+          <t>2108419</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>190834</t>
+          <t>218567</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152011</t>
+          <t>189032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>226927</t>
+          <t>258774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>276729</t>
+          <t>317833</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>228617</t>
+          <t>286074</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>315698</t>
+          <t>351492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4115,32 +4115,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>467563</t>
+          <t>536400</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>403907</t>
+          <t>491092</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>519745</t>
+          <t>584145</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4158,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3268983</t>
+          <t>3314195</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3232890</t>
+          <t>3273988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3307806</t>
+          <t>3343730</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3381129</t>
+          <t>3410056</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3342160</t>
+          <t>3376397</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3429241</t>
+          <t>3441815</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4228,32 +4228,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6650112</t>
+          <t>6724251</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6597930</t>
+          <t>6676506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6713768</t>
+          <t>6769559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657858</t>
+          <t>3727889</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657858</t>
+          <t>3727889</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657858</t>
+          <t>3727889</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7117675</t>
+          <t>7260651</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7117675</t>
+          <t>7260651</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7117675</t>
+          <t>7260651</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
